--- a/2_data_augmentation/human_annotations/manual_eval_files/manual_evaluation_dialogues.xlsx
+++ b/2_data_augmentation/human_annotations/manual_eval_files/manual_evaluation_dialogues.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,20 +448,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_sarcasm_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_sarcasm_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -470,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>103_1024</t>
+          <t>120_1045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,27 +475,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Steve says he wants to be young and cool, so he impulsively tries to post a picture on social media, but fails because he doesn't know how.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sure try again</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I don't get it, what do I do now? I thought I just had to click the post button.",
-    "u2": "Just click the share button, not the post button."
-  },
-  {
-    "u1": "I clicked the share button, but nothing happened. What now?",
-    "u2": "sure try again"
+          <t>{
+  "context": "Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, \"don't pressure me! I'm working on it, alright?\"",
+  "reply": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I don't know what you want from me, okay? I'm doing my best here.",
+    "u2": "Come on, Steve, that's not what I'm asking. I'm just trying to help."
+  },
+  {
+    "u1": "don't pressure me! I'm working on it, alright?",
+    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
   }
 ]</t>
         </is>
@@ -509,7 +502,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>120_1045</t>
+          <t>122_1050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -519,27 +512,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, "don't pressure me! I'm working on it, alright?"</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I don't know what you want from me, okay? I'm doing my best here.",
-    "u2": "Come on, Steve, that's not what I'm asking. I'm just trying to help."
-  },
-  {
-    "u1": "don't pressure me! I'm working on it, alright?",
-    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+          <t>{
+  "context": "You've just introduced Steve to your work colleagues and everybody seems to love him because he is funny, witty, and charming.  Steve says, \"hey, this is fun. I'm having a great time.\"",
+  "reply": "I knew you'd like them!"
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm really glad you're fitting in so well here. You're making a great impression.",
+    "u2": "I told you they'd love you!"
+  },
+  {
+    "u1": "hey, this is fun. I'm having a great time.",
+    "u2": "I knew you'd like them!"
   }
 ]</t>
         </is>
@@ -548,7 +539,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>203_2086</t>
+          <t>129_1007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,27 +549,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>That is hilarious Steve. Great imagination.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've got the best part of drawing a unicorn - the creativity! I'm thinking of adding a carrot to its forehead. It'll be the most majestic unicorn ever!",
-    "u2": "That's a great idea Steve! You're a genius when it comes to thinking outside the box."
-  },
-  {
-    "u1": "now that's a unicorn!",
-    "u2": "That is hilarious Steve. Great imagination."
+          <t>{
+  "context": "You are helping Steve move into a new apartment. After an hour, you realize that Steve is only carrying light stuff and you are doing all the heavy lifting.  Steve says, \"ugh, moving is always so stressful and chaotic...\"",
+  "reply": "Yes, this bit is always long to do."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I swear, I'm doing all the heavy lifting here. Can't you just help me out with the heavier stuff?",
+    "u2": "Yeah, I'm just trying to get everything in order."
+  },
+  {
+    "u1": "ugh, moving is always so stressful and chaotic...",
+    "u2": "Yes, this bit is always long to do."
   }
 ]</t>
         </is>
@@ -587,28 +576,100 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>205_2074</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "hey, look, I made something delicious!",
+    "u2": "what the hell is that?!"
+  },
+  {
+    "u1": "it's got ketchup, mustard, potato chips, and orange juice, it's gonna be a game changer!",
+    "u2": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>207_2112</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are watching TV with Steve. Whenever you set the volume to an odd number, Steve takes the remote control away from you and sets the volume to an even number.",
+  "reply": "Steve, have you ever considered seeing a therapist about OCD?"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "You're really getting good at this, but I'm still not letting you control the volume. You're going to give yourself a headache.",
+    "u2": "You're just trying to distract me so you can change the channel."
+  },
+  {
+    "u1": "I'm just trying to help you with the volume, okay?",
+    "u2": "Steve, have you ever considered seeing a therapist about OCD?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>215_2027</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Steve says to you, "have you noticed that kids these days drink energy drinks all the time? That can't be healthy." At the same time, you notice that Steve is getting his 8th cup of coffee of the day.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve.</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve says to you, \"have you noticed that kids these days drink energy drinks all the time? That can't be healthy.\" At the same time, you notice that Steve is getting his 8th cup of coffee of the day.",
+  "reply": "Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve."
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -623,31 +684,29 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>221_2069</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, "look, it must be an alien because humans can't do that. What else could it be?"</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>I don't know, but it might be.  Did you see the circles that farmer found in his field?</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, \"look, it must be an alien because humans can't do that. What else could it be?\"",
+  "reply": "I don't know, but it might be.  Did you see the circles that farmer found in his field?"
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -662,31 +721,29 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>222_2046</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, "I finally found one you'll like! This one is really good. Come on!"</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>I doubt it but go ahead.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, \"I finally found one you'll like! This one is really good. Come on!\"",
+  "reply": "I doubt it but go ahead."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -701,70 +758,29 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>229_2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>You and Steve are drinking at a bar. You both have had about 5 beers so far. Every single time you stand up to get more beer, Steve stops you and says, "get another one for me too, will you?"</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sure, but you owe me.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "Get another one for me too, will you?",
-    "u2": "I'm not your personal beer butler, get it yourself!"
-  },
-  {
-    "u1": "Get another one for me too, will you?",
-    "u2": "Sure, but you owe me."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>258_2046</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say "why can't you get it yourself?", he simply says, "oh, no reason. I just wanted you to do it for me."</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Well tough, get it yourself.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say \"why can't you get it yourself?\", he simply says, \"oh, no reason. I just wanted you to do it for me.\"",
+  "reply": "Well tough, get it yourself."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -779,31 +795,29 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>267_2115</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>You walk into the room and Steve is there and Steve says "hi!"</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You walk into the room and Steve is there and Steve says \"hi!\"",
+  "reply": "hello"
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -818,45 +832,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>271_2056</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>You are going to a party later today. You ask if Steve wants to join. He says, "I'm interested. When does the party start?"</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>about 9pm</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "What's the party like? Are there going to be a lot of people?",
-    "u2": "Yeah, I think so. I've heard it's going to be pretty big."
-  },
-  {
-    "u1": "When does the party start?",
-    "u2": "about 9pm"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -870,18 +845,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>I'm letting you win!</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "I'm letting you win!"
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>[
   {
@@ -909,18 +882,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>yaaaa because you are on the winning streak today enjoy while it last</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "yaaaa because you are on the winning streak today enjoy while it last"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>[
   {
@@ -948,18 +919,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>yawn</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+          <t>{
+  "context": "Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.",
+  "reply": "yawn"
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>[
   {
@@ -987,18 +956,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, "so, how is my puppy doing?"</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
+          <t>{
+  "context": "You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, \"so, how is my puppy doing?\"",
+  "reply": "I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>[
   {
@@ -1026,18 +993,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>an unusual one!</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
+          <t>{
+  "context": "Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, \"now that's a unicorn!\"",
+  "reply": "an unusual one!"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>[
   {
@@ -1055,7 +1020,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>205_2045</t>
+          <t>205_2055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1065,27 +1030,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says "hey, look, I made something delicious!"</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Knock yourself out, just don't expect me to try it!</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm telling you, it's a masterpiece! I've mixed the perfect combination of flavors and textures. You have to try it!",
-    "u2": "Dude, you're drunk. Maybe you should stick to making your famous five-alarm chili."
-  },
-  {
-    "u1": "Hey, look, I made something delicious!",
-    "u2": "Knock yourself out, just don't expect me to try it!"
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Yeah nah I'm good, you can have that yourself!"
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "What the heck is that you're making, Steve?",
+    "u2": "Mate, I'm trying to create something new, don't be a party pooper!"
+  },
+  {
+    "u1": "hey, look, I made something delicious!",
+    "u2": "Yeah nah I'm good, you can have that yourself!"
   }
 ]</t>
         </is>
@@ -1104,18 +1067,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, "wow, you really should watch how you spend your money."</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours.</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
+          <t>{
+  "context": "Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, \"wow, you really should watch how you spend your money.\"",
+  "reply": "Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours."
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>[
   {
@@ -1143,18 +1104,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say "I don't care. Just pick one and get it over with," Steve says "I don't need a haircut right now. But I want to be well-informed when I do!"</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
+          <t>{
+  "context": "Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say \"I don't care. Just pick one and get it over with,\" Steve says \"I don't need a haircut right now. But I want to be well-informed when I do!\"",
+  "reply": "Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>[
   {
@@ -1172,28 +1131,63 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>237_2038</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Did you really need to add orange juice to it?"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "hey, look, I made something delicious!",
+    "u2": "What is that abomination you've created?"
+  },
+  {
+    "u1": "This is going to be great, trust me!",
+    "u2": "Did you really need to add orange juice to it?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>242_2095</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, "jeez, people are so unreliable!"</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>yeah imagine that eh?</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, \"jeez, people are so unreliable!\"",
+  "reply": "yeah imagine that eh?"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
@@ -1203,45 +1197,6 @@
   {
     "u1": "Jeez, people are so unreliable!",
     "u2": "yeah imagine that eh?"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>248_2085</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Steve is learning French. Whenever Steve meets a French person, he speaks French to them but he is very bad at it. You and Steve met a person who doesn't speak English that well. And Steve whispers to you, "that person should work on their English, don't you think?"</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>I think you should work on your french</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I don't think that's a good idea, he's not even fluent in English, we should be more understanding.",
-    "u2": "I think you're not fluent in French"
-  },
-  {
-    "u1": "But he should still try to improve his English, right?",
-    "u2": "I think you should work on your french"
   }
 ]</t>
         </is>
@@ -1258,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1274,20 +1229,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_irony_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_irony_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -1306,18 +1256,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>@USER It's cruel and it's false</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+          <t>{
+  "post": "@USER It's cruel and it's false",
+  "reply": "@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny."
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>[
   {
@@ -1345,19 +1293,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&gt;the Commonwealth was trying to provide the manifest "as urgently as they possibly can"
-What the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>I know, this is totally unacceptable considering how hard Peter Dutton touts national security.</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>{
+  "post": "&gt;the Commonwealth was trying to provide the manifest \"as urgently as they possibly can\"\nWhat the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.",
+  "reply": "I know, this is totally unacceptable considering how hard Peter Dutton touts national security."
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>[
   {
@@ -1385,18 +1330,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>{
+  "post": "It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.",
+  "reply": "I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>[
   {
@@ -1424,28 +1367,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Q3. What is the resolution of the #GalaxyZFlip3 main camera?
-A. 8MP
-B. 10MP
-C. 12MP
-D. 16MP
-#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>@USER Q3) C. 12MP ?
-#GalaxyZFlip3 
-#FlipAtFlipkart #GalaxyZFlip3 
-#GalaxyZFlip3Giveaway 
-#stufflistingsarmy 
-@stufflistings</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>{
+  "post": "Q3. What is the resolution of the #GalaxyZFlip3 main camera?\nA. 8MP\nB. 10MP\nC. 12MP\nD. 16MP\n\n#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy",
+  "reply": "@USER Q3) C. 12MP ?\n\n#GalaxyZFlip3 \n#FlipAtFlipkart #GalaxyZFlip3 \n#GalaxyZFlip3Giveaway \n#stufflistingsarmy \n@stufflistings"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>[
   {
@@ -1473,18 +1404,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Okay that is HELLA interesting</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+          <t>{
+  "post": "Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)",
+  "reply": "Okay that is HELLA interesting"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>[
   {
@@ -1512,18 +1441,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+          <t>{
+  "post": "@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?",
+  "reply": "@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me"
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -1551,18 +1478,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I have COVID, I live alone and I am very sad. Please send pictures of your dogs.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
+          <t>{
+  "post": "I have COVID, I live alone and I am very sad. Please send pictures of your dogs.",
+  "reply": "@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon."
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -1590,18 +1515,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Please tell me that's photo-shopped.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>It's photoshopped.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+          <t>{
+  "post": "Please tell me that's photo-shopped.",
+  "reply": "It's photoshopped."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -1629,18 +1552,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+          <t>{
+  "post": "I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck",
+  "reply": "I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -1668,24 +1589,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The people of Scotland had a vote on devolution in 1997.
-They voted clearly in support of devolution and that vote has been respected with it's implementation.
-Time for another vote to see if they still want devolution.
-A lot has changed since then.
-Is that how it works?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>@USER One question . 
-SHOULD SCOTLAND BE INDEPENDENT.
-Ban all coverage from any political parties, let the people decide with their own conscience.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+          <t>{
+  "post": "The people of Scotland had a vote on devolution in 1997.\nThey voted clearly in support of devolution and that vote has been respected with it's implementation.\nTime for another vote to see if they still want devolution.\nA lot has changed since then.\nIs that how it works?",
+  "reply": "@USER One question . \n\nSHOULD SCOTLAND BE INDEPENDENT.\n\nBan all coverage from any political parties, let the people decide with their own conscience."
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -1703,7 +1616,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15884021082988968900_244264240786502817</t>
+          <t>15552971381088866001_11888329237387000433</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1713,28 +1626,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Counting calories as a strategy to lose weight generally never works.   
-Plus your eating low calorie ranch,  which is probably worse for your health at the end of the day.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "Have you tried intermittent fasting? I found it really helpful for weight loss. I also try to drink a lot of water throughout the day. It's really easy to get dehydrated if you're not careful.",
-    "u2": "I don't think that's a good idea. I've heard it can be bad for your health in the long run."
-  },
-  {
-    "u1": "The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.",
-    "u2": "Counting calories as a strategy to lose weight generally never works.   \nPlus your eating low calorie ranch,  which is probably worse for your health at the end of the day."
+          <t>{
+  "post": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+  "reply": "Lol. Nice one."
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Hey, have you seen this drone hovering around the area?",
+    "u2": "Nah, I haven't seen anything. What's up with it?"
+  },
+  {
+    "u1": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+    "u2": "Lol. Nice one."
   }
 ]</t>
         </is>
@@ -1743,7 +1653,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16479877604240977630_5093588245350490870</t>
+          <t>15878862390442679669_5355962305897979354</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1753,27 +1663,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>I guess it had the same sort of effect</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "What's the latest on the train situation?",
-    "u2": "Not sure, but I heard there was some kind of incident on the tracks"
-  },
-  {
-    "u1": "It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.",
-    "u2": "I guess it had the same sort of effect"
+          <t>{
+  "post": "It’s Official! I’m Irish!",
+  "reply": "Paper Irish*"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I just got back from a week-long trip to Ireland and I'm still on a high from the craic!",
+    "u2": "Craic agus ceol, I take it?"
+  },
+  {
+    "u1": "It’s Official! I’m Irish!",
+    "u2": "Paper Irish*"
   }
 ]</t>
         </is>
@@ -1782,28 +1690,137 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>16839627327148929126_1096202613083543084</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Resulting riots in carlow have caused literally dozens of euros in damage",
+  "reply": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm still trying to wrap my head around the news from Carlow. What's the latest?",
+    "u2": "Apparently, there was a bit of a disturbance in the town centre. Some people got a bit carried away and things escalated quickly."
+  },
+  {
+    "u1": "Resulting riots in carlow have caused literally dozens of euros in damage",
+    "u2": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>17330182337901269040_13248394110397545835</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+  "reply": "@USER And stay empty stomach, jobless."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "We should be proud of our country's rich history and heritage. It's time we give it the recognition it deserves. What do you think about the recent developments in our country's tourism sector?",
+    "u2": "tourism sector? Are you kidding me?"
+  },
+  {
+    "u1": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+    "u2": "@USER And stay empty stomach, jobless."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>17457646054318905579_2168687590666378141</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{
+  "post": "What is one company you'll never do business with because of their horrible politics?",
+  "reply": "@USER The Catholic Church"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Have you ever noticed how some companies seem to have a certain... let's call it 'vibe'?",
+    "u2": "I know what you mean. Some places just feel off to me."
+  },
+  {
+    "u1": "What is one company you'll never do business with because of their horrible politics?",
+    "u2": "@USER The Catholic Church"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2897406339829303586_14245870496726293002</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>@USER You missed  @USER  of the list.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>@USER  @USER Nah Jim bounces well.</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{
+  "post": "@USER You missed  @USER  of the list.",
+  "reply": "@USER  @USER Nah Jim bounces well."
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>[
   {
@@ -1818,128 +1835,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>3359863154989737995_1780717056669965981</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Arsenic byproduct of mining</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>That doesn't seem very fast acting.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "\"I've been reading about the effects of mining on the environment. It's really disturbing.",
-    "u2": "What kind of effects?"
-  },
-  {
-    "u1": "Arsenic byproduct of mining",
-    "u2": "That doesn't seem very fast acting."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3387143640398978761_8608797291134632917</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dear  @USER 
- I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I just got back from the National Games in Gujarat and I am still fuming about the experience I had with the airline staff. They were completely unhelpful and made us feel like we were a nuisance.",
-    "u2": "@USER I have had similar experiences with airline staff. They seem to think they are above the law and can treat customers however they like."
-  },
-  {
-    "u1": "Dear  @USER \n\n I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.",
-    "u2": "@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4153912052076221148_13253936608490326173</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>@USER Except for the fact that he is a cheat</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "It's unfortunate that the media is focusing on the negative aspects of the game, rather than the skills and talents of the players.",
-    "u2": "I'm not sure I agree. I think the media is just trying to tell it like it is."
-  },
-  {
-    "u1": "The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.",
-    "u2": "@USER Except for the fact that he is a cheat"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4406816020059779237_11047491654451679497</t>
+          <t>3323520100287981446_1413281847757410776</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1949,27 +1848,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jason Momoa, i'm straight but if i had to, that guy could tear me up.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ouch your butt</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm not sure what's more impressive, Jason Momoa's acting skills or his physique.",
-    "u2": "Girl, please. He's got a great face too"
-  },
-  {
-    "u1": "Jason Momoa, i'm straight but if i had to, that guy could tear me up.",
-    "u2": "Ouch your butt"
+          <t>{
+  "post": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+  "reply": "And are a security nightmare"
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm not sure I'd trust these smart home devices to make my life easier. I mean, how many times have we seen stories about them being hacked and used to spy on people?",
+    "u2": "Well, I think they're actually pretty safe. I've got a smart thermostat and it's been great. I can control it from my phone and it learns my schedule so it knows when to turn on and off."
+  },
+  {
+    "u1": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+    "u2": "And are a security nightmare"
   }
 ]</t>
         </is>
@@ -1978,7 +1875,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5529300028522332247_13762710351753037022</t>
+          <t>4377701867540598223_265041111922432154</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1988,27 +1885,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fuck me! The Russian Gollum has announced partial mobilisation!</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I just saw the news about Ukraine and I'm getting really worried. What's going on?",
-    "u2": "I know, it's all getting very serious. I've been following the updates on BBC News."
-  },
-  {
-    "u1": "Fuck me! The Russian Gollum has announced partial mobilisation!",
-    "u2": "@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!"
+          <t>{
+  "post": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+  "reply": "What's their excuse this time?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "\"Metro stations are the new battlegrounds for protests.",
+    "u2": "Is that what they're saying?"
+  },
+  {
+    "u1": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+    "u2": "What's their excuse this time?"
   }
 ]</t>
         </is>
@@ -2017,7 +1912,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>848231709404136191_17349058094094593523</t>
+          <t>5484529351205990135_6006195789051494887</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2027,27 +1922,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How many roads must a man walk down?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>The only word I know is grunt and I can't spell it.</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been thinking about my next big adventure and I'm torn between exploring the city or taking a road trip to the countryside.",
-    "u2": "Why are you even considering the city? It's all concrete and noise."
-  },
-  {
-    "u1": "How many roads must a man walk down?",
-    "u2": "The only word I know is grunt and I can't spell it."
+          <t>{
+  "post": "I know it says great, but all I see is ordinary Britain.",
+  "reply": "Ordinary Britain is in France"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm not sure what all the fuss is about. I just don't see the hype around this new travel destination.",
+    "u2": "You're not seeing it because you're not looking at it from the right perspective"
+  },
+  {
+    "u1": "I know it says great, but all I see is ordinary Britain.",
+    "u2": "Ordinary Britain is in France"
   }
 ]</t>
         </is>
@@ -2066,18 +1959,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>your son is brilliant</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
+          <t>{
+  "post": "My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.",
+  "reply": "your son is brilliant"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
@@ -2103,7 +1994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2119,20 +2010,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_sarcasm_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_sarcasm_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -2141,7 +2027,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>103_1024</t>
+          <t>120_1045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2151,31 +2037,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Steve says he wants to be young and cool, so he impulsively tries to post a picture on social media, but fails because he doesn't know how.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sure try again</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've got it! I'm going to post a picture of me doing a sick skateboard trick and get a million likes!",
-    "u2": "Dude, you can't even post a selfie, how are you going to post a picture of yourself doing a skateboard trick?"
-  },
-  {
-    "u1": "I don't know, just figure it out, I'm sure it can't be that hard!",
-    "u2": "Steve, you're going to end up looking like a total idiot if you post a picture of yourself trying to skateboard."
-  },
-  {
-    "u1": "I'm not going to look like an idiot, I'm going to be a total boss!",
-    "u2": "sure try again"
+          <t>{
+  "context": "Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, \"don't pressure me! I'm working on it, alright?\"",
+  "reply": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "don't pressure me! I'm working on it, alright?",
+    "u2": "Come on, Steve, don't give me that. What's really going on with that project?"
+  },
+  {
+    "u1": "I'm just taking my time, okay?",
+    "u2": "That's not what I'm asking, Steve. Is there something specific that's holding you back?"
+  },
+  {
+    "u1": "don't pressure me! I'm working on it, alright?",
+    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
   }
 ]</t>
         </is>
@@ -2184,7 +2068,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>120_1045</t>
+          <t>122_1050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2194,31 +2078,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, "don't pressure me! I'm working on it, alright?"</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "don't pressure me! I'm working on it, alright?",
-    "u2": "Come on, Steve, don't give me that. What's really going on with that project?"
-  },
-  {
-    "u1": "I'm just taking my time, okay?",
-    "u2": "That's not what I'm asking, Steve. Is there something specific that's holding you back?"
-  },
-  {
-    "u1": "don't pressure me! I'm working on it, alright?",
-    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+          <t>{
+  "context": "You've just introduced Steve to your work colleagues and everybody seems to love him because he is funny, witty, and charming.  Steve says, \"hey, this is fun. I'm having a great time.\"",
+  "reply": "I knew you'd like them!"
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "You're really fitting in well. Everyone seems to be enjoying your jokes.",
+    "u2": "I'm glad you're having fun!"
+  },
+  {
+    "u1": "I'm loving the vibe here. Your colleagues are great!",
+    "u2": "I told you they'd like you!"
+  },
+  {
+    "u1": "hey, this is fun. I'm having a great time.",
+    "u2": "I knew you'd like them!"
   }
 ]</t>
         </is>
@@ -2227,7 +2109,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>203_2086</t>
+          <t>129_1007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2237,31 +2119,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>That is hilarious Steve. Great imagination.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm going to draw a unicorn. It's going to be the most majestic thing you've ever seen.",
-    "u2": "You're such a goofball, Steve. Can't wait to see it."
-  },
-  {
-    "u1": "Okay, it's done! Behold, my masterpiece!",
-    "u2": "Huh? What's that supposed to be?"
-  },
-  {
-    "u1": "now that's a unicorn!",
-    "u2": "That is hilarious Steve. Great imagination."
+          <t>{
+  "context": "You are helping Steve move into a new apartment. After an hour, you realize that Steve is only carrying light stuff and you are doing all the heavy lifting.  Steve says, \"ugh, moving is always so stressful and chaotic...\"",
+  "reply": "Yes, this bit is always long to do."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm so glad we're doing this, I've been looking forward to moving into this new place for weeks!",
+    "u2": "I'm glad you're excited, but I'm starting to get a bit tired."
+  },
+  {
+    "u1": "Ugh, I'm not really carrying anything heavy, are you sure you're doing okay?",
+    "u2": "Yeah, I'm fine, just trying to get everything sorted out."
+  },
+  {
+    "u1": "ugh, moving is always so stressful and chaotic...",
+    "u2": "Yes, this bit is always long to do."
   }
 ]</t>
         </is>
@@ -2270,28 +2150,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>205_2074</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "hey, look, I made something delicious!",
+    "u2": "What the hell is that?"
+  },
+  {
+    "u1": "It's a new recipe, trust me, it's gonna be huge!",
+    "u2": "You can't even boil water, how are you gonna make a new recipe?"
+  },
+  {
+    "u1": "Hey, I'm just trying to be creative here!",
+    "u2": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>207_2112</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are watching TV with Steve. Whenever you set the volume to an odd number, Steve takes the remote control away from you and sets the volume to an even number.",
+  "reply": "Steve, have you ever considered seeing a therapist about OCD?"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "You're not going to believe this, but I just set the volume to 7. Again.",
+    "u2": "Seriously? You're doing that again. Can't you just let me control the TV for once?"
+  },
+  {
+    "u1": "Oh, come on. You were going to turn it up too loud. I'm just saving your hearing.",
+    "u2": "That's not the point. The point is you're always taking the remote away from me. It's getting old."
+  },
+  {
+    "u1": "You're being a bit dramatic, don't you think? It's just a TV remote.",
+    "u2": "Steve, have you ever considered seeing a therapist about OCD?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>215_2027</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Steve says to you, "have you noticed that kids these days drink energy drinks all the time? That can't be healthy." At the same time, you notice that Steve is getting his 8th cup of coffee of the day.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve.</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve says to you, \"have you noticed that kids these days drink energy drinks all the time? That can't be healthy.\" At the same time, you notice that Steve is getting his 8th cup of coffee of the day.",
+  "reply": "Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve."
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -2310,31 +2270,29 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>221_2069</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, "look, it must be an alien because humans can't do that. What else could it be?"</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>I don't know, but it might be.  Did you see the circles that farmer found in his field?</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, \"look, it must be an alien because humans can't do that. What else could it be?\"",
+  "reply": "I don't know, but it might be.  Did you see the circles that farmer found in his field?"
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -2353,31 +2311,29 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>222_2046</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, "I finally found one you'll like! This one is really good. Come on!"</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>I doubt it but go ahead.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, \"I finally found one you'll like! This one is really good. Come on!\"",
+  "reply": "I doubt it but go ahead."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -2396,74 +2352,29 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>229_2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>You and Steve are drinking at a bar. You both have had about 5 beers so far. Every single time you stand up to get more beer, Steve stops you and says, "get another one for me too, will you?"</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sure, but you owe me.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm gonna get another beer, you want one too?",
-    "u2": "No, I'm good."
-  },
-  {
-    "u1": "Alright, get me another one then.",
-    "u2": "You're buying, buddy."
-  },
-  {
-    "u1": "I'm gonna get another beer, you want one too?",
-    "u2": "Sure, but you owe me."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>258_2046</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say "why can't you get it yourself?", he simply says, "oh, no reason. I just wanted you to do it for me."</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Well tough, get it yourself.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say \"why can't you get it yourself?\", he simply says, \"oh, no reason. I just wanted you to do it for me.\"",
+  "reply": "Well tough, get it yourself."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -2482,31 +2393,29 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>267_2115</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>You walk into the room and Steve is there and Steve says "hi!"</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You walk into the room and Steve is there and Steve says \"hi!\"",
+  "reply": "hello"
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -2525,49 +2434,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>271_2056</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>You are going to a party later today. You ask if Steve wants to join. He says, "I'm interested. When does the party start?"</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>about 9pm</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "What time were you thinking of going to the party?",
-    "u2": "around 10"
-  },
-  {
-    "u1": "I'm not sure if I can make it that late, what's the earliest you could go?",
-    "u2": "around 9"
-  },
-  {
-    "u1": "I'm interested. When does the party start?",
-    "u2": "about 9pm"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -2581,18 +2447,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>I'm letting you win!</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "I'm letting you win!"
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>[
   {
@@ -2624,18 +2488,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>yaaaa because you are on the winning streak today enjoy while it last</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "yaaaa because you are on the winning streak today enjoy while it last"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>[
   {
@@ -2667,18 +2529,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>yawn</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+          <t>{
+  "context": "Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.",
+  "reply": "yawn"
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>[
   {
@@ -2710,18 +2570,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, "so, how is my puppy doing?"</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
+          <t>{
+  "context": "You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, \"so, how is my puppy doing?\"",
+  "reply": "I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>[
   {
@@ -2753,18 +2611,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>an unusual one!</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
+          <t>{
+  "context": "Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, \"now that's a unicorn!\"",
+  "reply": "an unusual one!"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>[
   {
@@ -2786,7 +2642,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>205_2045</t>
+          <t>205_2055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2796,31 +2652,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says "hey, look, I made something delicious!"</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Knock yourself out, just don't expect me to try it!</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I think I've got the secret to the perfect sauce! I'm just adding a bit more of that magic ingredient... orange juice!",
-    "u2": "You're not even kidding, are you?"
-  },
-  {
-    "u1": "Trust me, this is going to be epic! I'm basically a culinary genius!",
-    "u2": "Culinary genius? You're a culinary disaster waiting to happen!"
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Yeah nah I'm good, you can have that yourself!"
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Hey, look what I just mixed up! It's gonna be a real game-changer, I can feel it!",
+    "u2": "Mate, what have you done?"
+  },
+  {
+    "u1": "You gotta admit, this is a masterpiece! It's like a party in your mouth!",
+    "u2": "I don't know, Steve, I'm not really sure about this..."
   },
   {
     "u1": "Hey, look, I made something delicious!",
-    "u2": "Knock yourself out, just don't expect me to try it!"
+    "u2": "Yeah nah I'm good, you can have that yourself!"
   }
 ]</t>
         </is>
@@ -2839,18 +2693,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, "wow, you really should watch how you spend your money."</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours.</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
+          <t>{
+  "context": "Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, \"wow, you really should watch how you spend your money.\"",
+  "reply": "Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours."
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>[
   {
@@ -2882,18 +2734,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say "I don't care. Just pick one and get it over with," Steve says "I don't need a haircut right now. But I want to be well-informed when I do!"</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
+          <t>{
+  "context": "Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say \"I don't care. Just pick one and get it over with,\" Steve says \"I don't need a haircut right now. But I want to be well-informed when I do!\"",
+  "reply": "Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>[
   {
@@ -2915,28 +2765,67 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>237_2038</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Did you really need to add orange juice to it?"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm telling you, this is going to be a game-changer! Just mix all these amazing ingredients together and you get something truly unique.",
+    "u2": "I don't know, Steve, it looks like a mess to me."
+  },
+  {
+    "u1": "Come on, don't be a party pooper! I'm just experimenting with flavors and textures. It's going to be a hit, trust me.",
+    "u2": "You're really going to serve this to our guests?"
+  },
+  {
+    "u1": "Hey, look, I made something delicious!",
+    "u2": "Did you really need to add orange juice to it?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>242_2095</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, "jeez, people are so unreliable!"</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>yeah imagine that eh?</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, \"jeez, people are so unreliable!\"",
+  "reply": "yeah imagine that eh?"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
@@ -2950,49 +2839,6 @@
   {
     "u1": "Jeez, people are so unreliable!",
     "u2": "yeah imagine that eh?"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>248_2085</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Steve is learning French. Whenever Steve meets a French person, he speaks French to them but he is very bad at it. You and Steve met a person who doesn't speak English that well. And Steve whispers to you, "that person should work on their English, don't you think?"</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>I think you should work on your french</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I think that person is struggling with English, don't you think?",
-    "u2": "I think you should work on your french"
-  },
-  {
-    "u1": "I mean, I'm still learning French, but I'm sure I could help them with some basic phrases.",
-    "u2": "I think you should work on your french"
-  },
-  {
-    "u1": "that person should work on their English, don't you think?",
-    "u2": "I think you should work on your french"
   }
 ]</t>
         </is>
@@ -3009,7 +2855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3025,20 +2871,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_irony_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_irony_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -3057,18 +2898,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>@USER It's cruel and it's false</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+          <t>{
+  "post": "@USER It's cruel and it's false",
+  "reply": "@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny."
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>[
   {
@@ -3100,19 +2939,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&gt;the Commonwealth was trying to provide the manifest "as urgently as they possibly can"
-What the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>I know, this is totally unacceptable considering how hard Peter Dutton touts national security.</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>{
+  "post": "&gt;the Commonwealth was trying to provide the manifest \"as urgently as they possibly can\"\nWhat the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.",
+  "reply": "I know, this is totally unacceptable considering how hard Peter Dutton touts national security."
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>[
   {
@@ -3144,18 +2980,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>{
+  "post": "It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.",
+  "reply": "I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>[
   {
@@ -3187,28 +3021,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Q3. What is the resolution of the #GalaxyZFlip3 main camera?
-A. 8MP
-B. 10MP
-C. 12MP
-D. 16MP
-#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>@USER Q3) C. 12MP ?
-#GalaxyZFlip3 
-#FlipAtFlipkart #GalaxyZFlip3 
-#GalaxyZFlip3Giveaway 
-#stufflistingsarmy 
-@stufflistings</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>{
+  "post": "Q3. What is the resolution of the #GalaxyZFlip3 main camera?\nA. 8MP\nB. 10MP\nC. 12MP\nD. 16MP\n\n#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy",
+  "reply": "@USER Q3) C. 12MP ?\n\n#GalaxyZFlip3 \n#FlipAtFlipkart #GalaxyZFlip3 \n#GalaxyZFlip3Giveaway \n#stufflistingsarmy \n@stufflistings"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>[
   {
@@ -3240,18 +3062,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Okay that is HELLA interesting</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+          <t>{
+  "post": "Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)",
+  "reply": "Okay that is HELLA interesting"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>[
   {
@@ -3283,18 +3103,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+          <t>{
+  "post": "@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?",
+  "reply": "@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me"
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -3326,18 +3144,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I have COVID, I live alone and I am very sad. Please send pictures of your dogs.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
+          <t>{
+  "post": "I have COVID, I live alone and I am very sad. Please send pictures of your dogs.",
+  "reply": "@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon."
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -3369,18 +3185,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Please tell me that's photo-shopped.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>It's photoshopped.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+          <t>{
+  "post": "Please tell me that's photo-shopped.",
+  "reply": "It's photoshopped."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -3412,18 +3226,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+          <t>{
+  "post": "I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck",
+  "reply": "I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -3455,24 +3267,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The people of Scotland had a vote on devolution in 1997.
-They voted clearly in support of devolution and that vote has been respected with it's implementation.
-Time for another vote to see if they still want devolution.
-A lot has changed since then.
-Is that how it works?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>@USER One question . 
-SHOULD SCOTLAND BE INDEPENDENT.
-Ban all coverage from any political parties, let the people decide with their own conscience.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+          <t>{
+  "post": "The people of Scotland had a vote on devolution in 1997.\nThey voted clearly in support of devolution and that vote has been respected with it's implementation.\nTime for another vote to see if they still want devolution.\nA lot has changed since then.\nIs that how it works?",
+  "reply": "@USER One question . \n\nSHOULD SCOTLAND BE INDEPENDENT.\n\nBan all coverage from any political parties, let the people decide with their own conscience."
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -3494,7 +3298,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15884021082988968900_244264240786502817</t>
+          <t>15552971381088866001_11888329237387000433</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3504,32 +3308,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Counting calories as a strategy to lose weight generally never works.   
-Plus your eating low calorie ranch,  which is probably worse for your health at the end of the day.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been trying to lose some weight and I've noticed that when I eat smaller portions, I tend to feel more in control and less guilty about what I'm putting in my body.",
-    "u2": "That's just a temporary fix, you'll get bored and go back to your old habits."
-  },
-  {
-    "u1": "I've also been experimenting with different types of snacks to find ones that are both healthy and satisfying. I've found that crunchy veggies like carrots and celery are great because they fill me up without adding a lot of calories.",
-    "u2": "But don't you think that's just a form of restriction? You're still depriving yourself of certain foods."
-  },
-  {
-    "u1": "The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.",
-    "u2": "Counting calories as a strategy to lose weight generally never works.   \nPlus your eating low calorie ranch,  which is probably worse for your health at the end of the day."
+          <t>{
+  "post": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+  "reply": "Lol. Nice one."
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Just got back from a trip and I'm still finding stuff I lost. Anyone lost a phone recently?",
+    "u2": "Nah, I haven't lost anything"
+  },
+  {
+    "u1": "I'm starting to think I'm the only one who loses things all the time",
+    "u2": "Ha! You're just clumsy"
+  },
+  {
+    "u1": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+    "u2": "Lol. Nice one."
   }
 ]</t>
         </is>
@@ -3538,7 +3339,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16479877604240977630_5093588245350490870</t>
+          <t>15878862390442679669_5355962305897979354</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3548,31 +3349,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>I guess it had the same sort of effect</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm so glad I'm not the only one who saw that crazy thing on the tracks.",
-    "u2": "What are you talking about? I've been stuck in traffic all day."
-  },
-  {
-    "u1": "Apparently, it was some kind of vehicle that got stuck on the tracks.",
-    "u2": "Oh yeah? What kind of vehicle?"
-  },
-  {
-    "u1": "It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.",
-    "u2": "I guess it had the same sort of effect"
+          <t>{
+  "post": "It’s Official! I’m Irish!",
+  "reply": "Paper Irish*"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Just got my Irish citizenship! I've always wanted to connect with my heritage.",
+    "u2": "Congrats! How long did it take you to get the paperwork done?"
+  },
+  {
+    "u1": "It was a long process, but totally worth it! I'm so excited to celebrate St. Patrick's Day this year!",
+    "u2": "You'll have to show me your new passport. I want to see the 'Irish' stamp."
+  },
+  {
+    "u1": "It’s Official! I’m Irish!",
+    "u2": "Paper Irish*"
   }
 ]</t>
         </is>
@@ -3581,28 +3380,149 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>16839627327148929126_1096202613083543084</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Resulting riots in carlow have caused literally dozens of euros in damage",
+  "reply": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Carlow is really going off tonight, what's the situation like on the ground?",
+    "u2": "It's absolute chaos. People are smashing windows and setting fire to bins. I'm not even kidding, it's like the end of the world."
+  },
+  {
+    "u1": "I just saw a group of lads smashing up a shop on Barrack St. What's the police doing about it?",
+    "u2": "To be honest, I've seen about 5 cops in the entire town. They're just standing around looking helpless. It's like they're waiting for someone else to sort it out."
+  },
+  {
+    "u1": "Resulting riots in carlow have caused literally dozens of euros in damage",
+    "u2": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>17330182337901269040_13248394110397545835</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+  "reply": "@USER And stay empty stomach, jobless."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "It's time to make a change in India. We need to see some action from our leaders. I'm calling out to all Congressmen out there: let's see some transparency and accountability.",
+    "u2": "What action do you want from them?"
+  },
+  {
+    "u1": "I want to know if they've visited the Statue of Unity. It's a symbol of our nation's progress, and I think it's only fair that they show some interest in it.",
+    "u2": "Maybe they're too busy to care about some statue."
+  },
+  {
+    "u1": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+    "u2": "@USER And stay empty stomach, jobless."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>17457646054318905579_2168687590666378141</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{
+  "post": "What is one company you'll never do business with because of their horrible politics?",
+  "reply": "@USER The Catholic Church"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "u1: What do you think about the role of religion in politics? Should they be separate?",
+    "u2": "Absolutely, they should be separate. Religion is personal and should not influence public policy."
+  },
+  {
+    "u1": "But what about companies that use their religion as a way to justify discriminatory practices?",
+    "u2": "That's a whole different story. I think companies should be held accountable for their actions and policies, regardless of their religious affiliations."
+  },
+  {
+    "u1": "What is one company you'll never do business with because of their horrible politics?",
+    "u2": "@USER The Catholic Church"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2897406339829303586_14245870496726293002</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>@USER You missed  @USER  of the list.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>@USER  @USER Nah Jim bounces well.</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{
+  "post": "@USER You missed  @USER  of the list.",
+  "reply": "@USER  @USER Nah Jim bounces well."
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>[
   {
@@ -3621,140 +3541,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>3359863154989737995_1780717056669965981</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Arsenic byproduct of mining</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>That doesn't seem very fast acting.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been reading about the environmental impact of mining and I'm getting a bit worried.",
-    "u2": "What's got you concerned?"
-  },
-  {
-    "u1": "Apparently, some mining processes release toxic chemicals into the water and soil.",
-    "u2": "That's terrible. Do you think it's a widespread problem?"
-  },
-  {
-    "u1": "Arsenic byproduct of mining",
-    "u2": "That doesn't seem very fast acting."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3387143640398978761_8608797291134632917</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dear  @USER 
- I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm still fuming about the National Games in Gujarat. The organizers were so unprepared, and the accommodation was a nightmare. I'm an athlete, and I expect a certain level of respect and care.",
-    "u2": "@USER What's the big deal? It's just a game, right?"
-  },
-  {
-    "u1": "I'm not just talking about the games themselves, but the way we were treated as a whole. The staff at the airport, the food, the transportation... everything was a disaster. And to top it all off, they charged us for excess baggage for our medals and goodies!",
-    "u2": "@USER Oh, come on! You're an athlete, you must be used to dealing with some level of chaos. It's not like you're a celebrity or something."
-  },
-  {
-    "u1": "Dear  @USER \n\n I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.",
-    "u2": "@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4153912052076221148_13253936608490326173</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>@USER Except for the fact that he is a cheat</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm getting a bit tired of the constant scrutiny on young players. It's hard enough to make it in this game without having the media breathing down your neck.",
-    "u2": "Why are you defending him? He's clearly not playing by the rules"
-  },
-  {
-    "u1": "I'm not defending him, I'm just saying that we should be more understanding and not jump to conclusions. We've all made mistakes on the field, right?",
-    "u2": "Mistakes? He's been caught red-handed multiple times, it's not a mistake, it's a pattern of behaviour"
-  },
-  {
-    "u1": "The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.",
-    "u2": "@USER Except for the fact that he is a cheat"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4406816020059779237_11047491654451679497</t>
+          <t>3323520100287981446_1413281847757410776</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3764,31 +3554,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jason Momoa, i'm straight but if i had to, that guy could tear me up.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ouch your butt</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "Jason Momoa's got some serious brawn going on, right?",
-    "u2": "I know, I saw him in that Aquaman movie"
-  },
-  {
-    "u1": "He's like a real-life superhero, but with a better beard",
-    "u2": "Haha yeah, and a better abs too"
-  },
-  {
-    "u1": "Jason Momoa, i'm straight but if i had to, that guy could tear me up.",
-    "u2": "Ouch your butt"
+          <t>{
+  "post": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+  "reply": "And are a security nightmare"
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm not sure what's more annoying, the constant stream of smart devices trying to 'improve' our lives or the fact that they're all just a bunch of unnecessary clutter.",
+    "u2": "I see what you mean, but some of these devices can be really convenient. I mean, having a smart thermostat that learns your schedule and preferences is pretty cool."
+  },
+  {
+    "u1": "But at what point do we draw the line? Do we really need a smart coffee maker that can order beans online and schedule brewing times?",
+    "u2": "Well, I think it's all about finding a balance between convenience and security. I mean, if these devices are connected to the internet, they're basically a vulnerability waiting to happen."
+  },
+  {
+    "u1": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+    "u2": "And are a security nightmare"
   }
 ]</t>
         </is>
@@ -3797,7 +3585,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5529300028522332247_13762710351753037022</t>
+          <t>4377701867540598223_265041111922432154</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3807,31 +3595,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fuck me! The Russian Gollum has announced partial mobilisation!</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm getting a bad feeling about this. The Russian government's been acting really strange lately. I'm starting to think they're planning something big.",
-    "u2": "I know what you mean. I've been following the news, and it seems like they're getting more aggressive by the day."
-  },
-  {
-    "u1": "Do you think it's possible that they're planning to invade Ukraine again? I've heard rumors that they're mobilizing their military.",
-    "u2": "I don't know, but I do know that their president has been making some pretty scary statements lately. I'm getting a little worried."
-  },
-  {
-    "u1": "Fuck me! The Russian Gollum has announced partial mobilisation!",
-    "u2": "@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!"
+          <t>{
+  "post": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+  "reply": "What's their excuse this time?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "\"This is getting out of hand. We can't just let them shout at the metro stations.",
+    "u2": "I know, right? It's like they're trying to start a riot."
+  },
+  {
+    "u1": "It's not just the shouting. They're also vandalizing the stations.",
+    "u2": "That's it, I've had enough. We need to do something about this."
+  },
+  {
+    "u1": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+    "u2": "What's their excuse this time?"
   }
 ]</t>
         </is>
@@ -3840,7 +3626,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>848231709404136191_17349058094094593523</t>
+          <t>5484529351205990135_6006195789051494887</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3850,31 +3636,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How many roads must a man walk down?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>The only word I know is grunt and I can't spell it.</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm so tired of walking on the same old streets. I need a change of scenery.",
-    "u2": "What's wrong with the streets you have? They're fine, right?"
-  },
-  {
-    "u1": "No, they're just too familiar. I need to explore new places.",
-    "u2": "But don't you think that's just a waste of time?"
-  },
-  {
-    "u1": "How many roads must a man walk down?",
-    "u2": "The only word I know is grunt and I can't spell it."
+          <t>{
+  "post": "I know it says great, but all I see is ordinary Britain.",
+  "reply": "Ordinary Britain is in France"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I've been to Britain a few times and I have to say, I'm not blown away by it.",
+    "u2": "What do you mean? I think it's fantastic!"
+  },
+  {
+    "u1": "I don't know, it just feels so... ordinary. I mean, the food, the culture, the people... it all seems so... normal.",
+    "u2": "Normal? That's what I love about it! It's not all about the glitz and glamour, you know?"
+  },
+  {
+    "u1": "I know it says great, but all I see is ordinary Britain.",
+    "u2": "Ordinary Britain is in France"
   }
 ]</t>
         </is>
@@ -3893,18 +3677,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>your son is brilliant</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
+          <t>{
+  "post": "My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.",
+  "reply": "your son is brilliant"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
@@ -3934,7 +3716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3950,20 +3732,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_sarcasm_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_sarcasm_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -3972,7 +3749,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>103_1024</t>
+          <t>120_1045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3982,27 +3759,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Steve says he wants to be young and cool, so he impulsively tries to post a picture on social media, but fails because he doesn't know how.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sure try again</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm not sure how to do it, I tried to upload it but it didn't work. I think I'm not doing it right.",
-    "u2": "Okay, let me show you how."
-  },
-  {
-    "u1": "I'm not sure how to do it, I tried to upload it but it didn't work. I think I'm not doing it right.",
-    "u2": "sure try again"
+          <t>{
+  "context": "Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, \"don't pressure me! I'm working on it, alright?\"",
+  "reply": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm really trying to focus on this project, but it's just not coming together.",
+    "u2": "What's the holdup, mate? You've been at this for ages."
+  },
+  {
+    "u1": "It's just... really complicated. I'm having trouble figuring it out.",
+    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
   }
 ]</t>
         </is>
@@ -4011,7 +3786,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>120_1045</t>
+          <t>122_1050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4021,27 +3796,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, "don't pressure me! I'm working on it, alright?"</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm really trying to focus on this project, but it's just not coming together.",
-    "u2": "What's the holdup, mate? You've been at this for ages."
-  },
-  {
-    "u1": "It's just... really complicated. I'm having trouble figuring it out.",
-    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+          <t>{
+  "context": "You've just introduced Steve to your work colleagues and everybody seems to love him because he is funny, witty, and charming.  Steve says, \"hey, this is fun. I'm having a great time.\"",
+  "reply": "I knew you'd like them!"
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm really glad you introduced me to your colleagues. They seem like a great bunch!",
+    "u2": "I'm so glad you think so."
+  },
+  {
+    "u1": "You were right about them. I'm having a blast!",
+    "u2": "I knew you'd like them!"
   }
 ]</t>
         </is>
@@ -4050,7 +3823,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>203_2086</t>
+          <t>129_1007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4060,27 +3833,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>That is hilarious Steve. Great imagination.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been practicing my drawing. I think I'm ready for that unicorn now!",
-    "u2": "That's awesome Steve! I can't wait to see it."
-  },
-  {
-    "u1": "I drew a unicorn. Here it is!",
-    "u2": "That is hilarious Steve. Great imagination."
+          <t>{
+  "context": "You are helping Steve move into a new apartment. After an hour, you realize that Steve is only carrying light stuff and you are doing all the heavy lifting.  Steve says, \"ugh, moving is always so stressful and chaotic...\"",
+  "reply": "Yes, this bit is always long to do."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I can't believe we've been at this for so long already!",
+    "u2": "Yeah, I know what you mean."
+  },
+  {
+    "u1": "I've been carrying these boxes for what feels like hours!",
+    "u2": "Yes, this bit is always long to do."
   }
 ]</t>
         </is>
@@ -4089,28 +3860,100 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>205_2074</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm just trying to help! I thought I could make something everyone would enjoy.",
+    "u2": "You're not helping, Steve. Just stop."
+  },
+  {
+    "u1": "I'm just trying to help! I thought I could make something everyone would enjoy.",
+    "u2": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>207_2112</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are watching TV with Steve. Whenever you set the volume to an odd number, Steve takes the remote control away from you and sets the volume to an even number.",
+  "reply": "Steve, have you ever considered seeing a therapist about OCD?"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Steve: You know, I've been thinking about that. I might have a bit of a control issue with the TV volume.",
+    "u2": "Steve, that's a bit extreme. I mean, it's just a volume."
+  },
+  {
+    "u1": "You know, I've been thinking about that. I might have a bit of a control issue with the TV volume.",
+    "u2": "Steve, have you ever considered seeing a therapist about OCD?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>215_2027</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Steve says to you, "have you noticed that kids these days drink energy drinks all the time? That can't be healthy." At the same time, you notice that Steve is getting his 8th cup of coffee of the day.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve.</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve says to you, \"have you noticed that kids these days drink energy drinks all the time? That can't be healthy.\" At the same time, you notice that Steve is getting his 8th cup of coffee of the day.",
+  "reply": "Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve."
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -4125,31 +3968,29 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>221_2069</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, "look, it must be an alien because humans can't do that. What else could it be?"</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>I don't know, but it might be.  Did you see the circles that farmer found in his field?</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, \"look, it must be an alien because humans can't do that. What else could it be?\"",
+  "reply": "I don't know, but it might be.  Did you see the circles that farmer found in his field?"
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -4164,31 +4005,29 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>222_2046</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, "I finally found one you'll like! This one is really good. Come on!"</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>I doubt it but go ahead.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, \"I finally found one you'll like! This one is really good. Come on!\"",
+  "reply": "I doubt it but go ahead."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -4203,70 +4042,29 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>229_2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>You and Steve are drinking at a bar. You both have had about 5 beers so far. Every single time you stand up to get more beer, Steve stops you and says, "get another one for me too, will you?"</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sure, but you owe me.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm gonna need another one of these when you head back.",
-    "u2": "I'm getting another round, Steve."
-  },
-  {
-    "u1": "Get another one for me too, will you?",
-    "u2": "Sure, but you owe me."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>258_2046</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say "why can't you get it yourself?", he simply says, "oh, no reason. I just wanted you to do it for me."</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Well tough, get it yourself.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say \"why can't you get it yourself?\", he simply says, \"oh, no reason. I just wanted you to do it for me.\"",
+  "reply": "Well tough, get it yourself."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -4281,31 +4079,29 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>267_2115</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>You walk into the room and Steve is there and Steve says "hi!"</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You walk into the room and Steve is there and Steve says \"hi!\"",
+  "reply": "hello"
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -4320,45 +4116,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>271_2056</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>You are going to a party later today. You ask if Steve wants to join. He says, "I'm interested. When does the party start?"</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>about 9pm</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm definitely in! What time should I be there?",
-    "u2": "Around 7pm"
-  },
-  {
-    "u1": "About 9pm?",
-    "u2": "about 9pm"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -4372,18 +4129,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>I'm letting you win!</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "I'm letting you win!"
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>[
   {
@@ -4411,18 +4166,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>yaaaa because you are on the winning streak today enjoy while it last</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "yaaaa because you are on the winning streak today enjoy while it last"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>[
   {
@@ -4450,18 +4203,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>yawn</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+          <t>{
+  "context": "Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.",
+  "reply": "yawn"
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>[
   {
@@ -4489,18 +4240,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, "so, how is my puppy doing?"</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
+          <t>{
+  "context": "You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, \"so, how is my puppy doing?\"",
+  "reply": "I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>[
   {
@@ -4528,18 +4277,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>an unusual one!</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
+          <t>{
+  "context": "Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, \"now that's a unicorn!\"",
+  "reply": "an unusual one!"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>[
   {
@@ -4557,7 +4304,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>205_2045</t>
+          <t>205_2055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4567,27 +4314,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says "hey, look, I made something delicious!"</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Knock yourself out, just don't expect me to try it!</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "Hey, I've got an idea! Let's make some fun food for the party. I'm thinking we should try...",
-    "u2": "I'm not sure that's a good idea, Steve."
-  },
-  {
-    "u1": "How about mixing some ketchup and mustard? We could call it 'Steve's Special Sauce'!",
-    "u2": "Knock yourself out, just don't expect me to try it!"
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Yeah nah I'm good, you can have that yourself!"
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Hey, I made a new drink! It's called 'Orange Juice Surprise'. You want to try it?",
+    "u2": "No thanks, Steve, I'm good."
+  },
+  {
+    "u1": "Yeah, I made something delicious! You want to try it?",
+    "u2": "Yeah nah I'm good, you can have that yourself!"
   }
 ]</t>
         </is>
@@ -4606,18 +4351,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, "wow, you really should watch how you spend your money."</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours.</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
+          <t>{
+  "context": "Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, \"wow, you really should watch how you spend your money.\"",
+  "reply": "Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours."
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>[
   {
@@ -4645,18 +4388,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say "I don't care. Just pick one and get it over with," Steve says "I don't need a haircut right now. But I want to be well-informed when I do!"</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
+          <t>{
+  "context": "Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say \"I don't care. Just pick one and get it over with,\" Steve says \"I don't need a haircut right now. But I want to be well-informed when I do!\"",
+  "reply": "Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>[
   {
@@ -4674,28 +4415,63 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>237_2038</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Did you really need to add orange juice to it?"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Steve: Hey, check this out! I've got a new recipe for you guys.",
+    "u2": "Steve, are you sure that's a good idea?"
+  },
+  {
+    "u1": "Yep, I think it'll be great! I've got a secret ingredient.",
+    "u2": "Did you really need to add orange juice to it?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>242_2095</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, "jeez, people are so unreliable!"</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>yeah imagine that eh?</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, \"jeez, people are so unreliable!\"",
+  "reply": "yeah imagine that eh?"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
@@ -4705,45 +4481,6 @@
   {
     "u1": "Yeah, but it's been weeks now and no sign of it. People are so unreliable!",
     "u2": "yeah imagine that eh?"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>248_2085</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Steve is learning French. Whenever Steve meets a French person, he speaks French to them but he is very bad at it. You and Steve met a person who doesn't speak English that well. And Steve whispers to you, "that person should work on their English, don't you think?"</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>I think you should work on your french</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been practicing French, but I feel like I'm not getting better.",
-    "u2": "You're doing better than you think. Keep at it."
-  },
-  {
-    "u1": "I don't think I'm ready to talk to that person yet.",
-    "u2": "I think you should work on your french"
   }
 ]</t>
         </is>
@@ -4760,7 +4497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4776,20 +4513,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_irony_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_irony_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -4808,18 +4540,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>@USER It's cruel and it's false</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+          <t>{
+  "post": "@USER It's cruel and it's false",
+  "reply": "@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny."
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>[
   {
@@ -4847,19 +4577,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&gt;the Commonwealth was trying to provide the manifest "as urgently as they possibly can"
-What the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>I know, this is totally unacceptable considering how hard Peter Dutton touts national security.</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>{
+  "post": "&gt;the Commonwealth was trying to provide the manifest \"as urgently as they possibly can\"\nWhat the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.",
+  "reply": "I know, this is totally unacceptable considering how hard Peter Dutton touts national security."
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>[
   {
@@ -4887,18 +4614,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>{
+  "post": "It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.",
+  "reply": "I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>[
   {
@@ -4926,28 +4651,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Q3. What is the resolution of the #GalaxyZFlip3 main camera?
-A. 8MP
-B. 10MP
-C. 12MP
-D. 16MP
-#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>@USER Q3) C. 12MP ?
-#GalaxyZFlip3 
-#FlipAtFlipkart #GalaxyZFlip3 
-#GalaxyZFlip3Giveaway 
-#stufflistingsarmy 
-@stufflistings</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>{
+  "post": "Q3. What is the resolution of the #GalaxyZFlip3 main camera?\nA. 8MP\nB. 10MP\nC. 12MP\nD. 16MP\n\n#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy",
+  "reply": "@USER Q3) C. 12MP ?\n\n#GalaxyZFlip3 \n#FlipAtFlipkart #GalaxyZFlip3 \n#GalaxyZFlip3Giveaway \n#stufflistingsarmy \n@stufflistings"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>[
   {
@@ -4975,18 +4688,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Okay that is HELLA interesting</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+          <t>{
+  "post": "Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)",
+  "reply": "Okay that is HELLA interesting"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>[
   {
@@ -5014,18 +4725,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+          <t>{
+  "post": "@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?",
+  "reply": "@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me"
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -5053,18 +4762,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I have COVID, I live alone and I am very sad. Please send pictures of your dogs.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
+          <t>{
+  "post": "I have COVID, I live alone and I am very sad. Please send pictures of your dogs.",
+  "reply": "@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon."
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -5092,18 +4799,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Please tell me that's photo-shopped.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>It's photoshopped.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+          <t>{
+  "post": "Please tell me that's photo-shopped.",
+  "reply": "It's photoshopped."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -5131,18 +4836,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+          <t>{
+  "post": "I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck",
+  "reply": "I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -5170,24 +4873,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The people of Scotland had a vote on devolution in 1997.
-They voted clearly in support of devolution and that vote has been respected with it's implementation.
-Time for another vote to see if they still want devolution.
-A lot has changed since then.
-Is that how it works?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>@USER One question . 
-SHOULD SCOTLAND BE INDEPENDENT.
-Ban all coverage from any political parties, let the people decide with their own conscience.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+          <t>{
+  "post": "The people of Scotland had a vote on devolution in 1997.\nThey voted clearly in support of devolution and that vote has been respected with it's implementation.\nTime for another vote to see if they still want devolution.\nA lot has changed since then.\nIs that how it works?",
+  "reply": "@USER One question . \n\nSHOULD SCOTLAND BE INDEPENDENT.\n\nBan all coverage from any political parties, let the people decide with their own conscience."
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -5205,7 +4900,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15884021082988968900_244264240786502817</t>
+          <t>15552971381088866001_11888329237387000433</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5215,28 +4910,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Counting calories as a strategy to lose weight generally never works.   
-Plus your eating low calorie ranch,  which is probably worse for your health at the end of the day.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been trying to lose weight and I've been reading about counting calories. It seems to be a good strategy.",
-    "u2": "Counting calories can be helpful, but it's not the only way to lose weight. What about your diet? Are you eating a lot of processed foods?"
-  },
-  {
-    "u1": "The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.",
-    "u2": "Counting calories as a strategy to lose weight generally never works.   \nPlus your eating low calorie ranch,  which is probably worse for your health at the end of the day."
+          <t>{
+  "post": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+  "reply": "Lol. Nice one."
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I dropped a wallet in Central Park last week...",
+    "u2": "Oh, I'm sure it's not lost forever."
+  },
+  {
+    "u1": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+    "u2": "Lol. Nice one."
   }
 ]</t>
         </is>
@@ -5245,7 +4937,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16479877604240977630_5093588245350490870</t>
+          <t>15878862390442679669_5355962305897979354</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5255,27 +4947,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>I guess it had the same sort of effect</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "u1: I was just thinking about the incident with the train lines. You saw the news?",
-    "u2": "Yeah, I did. Quite a mess, huh?"
-  },
-  {
-    "u1": "It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.",
-    "u2": "I guess it had the same sort of effect"
+          <t>{
+  "post": "It’s Official! I’m Irish!",
+  "reply": "Paper Irish*"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I just got the confirmation! I'm officially Irish now!",
+    "u2": "That's awesome! How did you feel when you got the news?"
+  },
+  {
+    "u1": "It’s Official! I’m Irish!",
+    "u2": "Paper Irish*"
   }
 ]</t>
         </is>
@@ -5284,28 +4974,137 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>16839627327148929126_1096202613083543084</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Resulting riots in carlow have caused literally dozens of euros in damage",
+  "reply": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I heard there were some protests in Carlow today. How did they turn out?",
+    "u2": "Not so well. There was a riot, and a few shops got damaged."
+  },
+  {
+    "u1": "Resulting riots in carlow have caused literally dozens of euros in damage",
+    "u2": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>17330182337901269040_13248394110397545835</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+  "reply": "@USER And stay empty stomach, jobless."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "u1: @USER I'm curious, have you visited the Statue of Unity?",
+    "u2": "u2: @USER I haven't, but I'm not a fan of PM Modi's projects."
+  },
+  {
+    "u1": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+    "u2": "@USER And stay empty stomach, jobless."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>17457646054318905579_2168687590666378141</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{
+  "post": "What is one company you'll never do business with because of their horrible politics?",
+  "reply": "@USER The Catholic Church"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I've been thinking, what's one company you'd never do business with due to their politics?",
+    "u2": "That's a tough one. I'd say the Catholic Church."
+  },
+  {
+    "u1": "What is one company you'll never do business with because of their horrible politics?",
+    "u2": "@USER The Catholic Church"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2897406339829303586_14245870496726293002</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>@USER You missed  @USER  of the list.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>@USER  @USER Nah Jim bounces well.</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{
+  "post": "@USER You missed  @USER  of the list.",
+  "reply": "@USER  @USER Nah Jim bounces well."
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>[
   {
@@ -5320,128 +5119,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>3359863154989737995_1780717056669965981</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Arsenic byproduct of mining</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>That doesn't seem very fast acting.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been reading up on environmental impacts of mining. Have you heard about arsenic?",
-    "u2": "Oh, I know it's a concern, but what about it?"
-  },
-  {
-    "u1": "Arsenic byproduct of mining",
-    "u2": "That doesn't seem very fast acting."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3387143640398978761_8608797291134632917</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dear  @USER 
- I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm so tired after the long journey back from Gujarat. I'm sure you've heard about the National Games?",
-    "u2": "Yes, I heard it went well for you."
-  },
-  {
-    "u1": "Dear  @USER \n\n I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.",
-    "u2": "@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4153912052076221148_13253936608490326173</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>@USER Except for the fact that he is a cheat</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "u1: I think we need to focus more on the positives in the game. The media tends to highlight the negatives too much.",
-    "u2": "The negatives are there for a reason. We can't ignore the issues."
-  },
-  {
-    "u1": "The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.",
-    "u2": "@USER Except for the fact that he is a cheat"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4406816020059779237_11047491654451679497</t>
+          <t>3323520100287981446_1413281847757410776</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5451,27 +5132,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jason Momoa, i'm straight but if i had to, that guy could tear me up.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ouch your butt</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm a fan of Jason Momoa, but I'd never date him.",
-    "u2": "Why not?"
-  },
-  {
-    "u1": "Jason Momoa, i'm straight but if i had to, that guy could tear me up.",
-    "u2": "Ouch your butt"
+          <t>{
+  "post": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+  "reply": "And are a security nightmare"
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I've been looking into smart home devices and I'm surprised how many options there are for controlling your appliances with your phone.",
+    "u2": "That's true, but the convenience comes with risks."
+  },
+  {
+    "u1": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+    "u2": "And are a security nightmare"
   }
 ]</t>
         </is>
@@ -5480,7 +5159,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5529300028522332247_13762710351753037022</t>
+          <t>4377701867540598223_265041111922432154</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5490,27 +5169,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fuck me! The Russian Gollum has announced partial mobilisation!</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been watching the news and it's looking pretty grim.",
-    "u2": "Yeah, it's been a crazy day. I'm surprised they haven't declared martial law yet."
-  },
-  {
-    "u1": "Fuck me! The Russian Gollum has announced partial mobilisation!",
-    "u2": "@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!"
+          <t>{
+  "post": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+  "reply": "What's their excuse this time?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I saw someone shouting \"Goli Maro\" at the Metro Station today.",
+    "u2": "What's the context behind it?"
+  },
+  {
+    "u1": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+    "u2": "What's their excuse this time?"
   }
 ]</t>
         </is>
@@ -5519,7 +5196,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>848231709404136191_17349058094094593523</t>
+          <t>5484529351205990135_6006195789051494887</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5529,27 +5206,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How many roads must a man walk down?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>The only word I know is grunt and I can't spell it.</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "It's a beautiful day, isn't it? I've been thinking about the old song, 'Blowin' in the Wind'.",
-    "u2": "I don't know much about old songs, but I like the sound of 'grunt'."
-  },
-  {
-    "u1": "How many roads must a man walk down?",
-    "u2": "The only word I know is grunt and I can't spell it."
+          <t>{
+  "post": "I know it says great, but all I see is ordinary Britain.",
+  "reply": "Ordinary Britain is in France"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "u1: I'm not sure if I'm missing something, but this place seems quite normal to me.",
+    "u2": "That's because it is. It's just ordinary Britain."
+  },
+  {
+    "u1": "I know it says great, but all I see is ordinary Britain.",
+    "u2": "Ordinary Britain is in France"
   }
 ]</t>
         </is>
@@ -5568,18 +5243,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>your son is brilliant</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
+          <t>{
+  "post": "My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.",
+  "reply": "your son is brilliant"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
@@ -5605,7 +5278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5621,20 +5294,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>context</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_sarcasm_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_sarcasm_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -5643,7 +5311,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>103_1024</t>
+          <t>120_1045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5653,31 +5321,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Steve says he wants to be young and cool, so he impulsively tries to post a picture on social media, but fails because he doesn't know how.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>sure try again</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I just saw this cool filter on TikTok. I want to try it out!",
-    "u2": "That's cool, but I don't think you can use it on Facebook."
-  },
-  {
-    "u1": "Oh, really? How do I use it then?",
-    "u2": "You need to use Instagram or TikTok."
-  },
-  {
-    "u1": "Okay, I'll try it on Instagram then.",
-    "u2": "sure try again"
+          <t>{
+  "context": "Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, \"don't pressure me! I'm working on it, alright?\"",
+  "reply": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm just trying to get everything done before the deadline, okay? Don't worry about it.",
+    "u2": "You're not making it easy for me to not worry, Steve. What's the holdup?"
+  },
+  {
+    "u1": "It's just a lot of work, alright? I'm handling it.",
+    "u2": "Handling it? You've been 'handling it' for weeks now. I'm starting to get concerned."
+  },
+  {
+    "u1": "Come on, you're not my mom. I said I'm working on it!",
+    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
   }
 ]</t>
         </is>
@@ -5686,7 +5352,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>120_1045</t>
+          <t>122_1050</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5696,31 +5362,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Steve acts passive-aggressive no matter what you say these days. When you ask him whether he's made any progress on his final project,  Steve says, "don't pressure me! I'm working on it, alright?"</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm just trying to get everything done before the deadline, okay? Don't worry about it.",
-    "u2": "You're not making it easy for me to not worry, Steve. What's the holdup?"
-  },
-  {
-    "u1": "It's just a lot of work, alright? I'm handling it.",
-    "u2": "Handling it? You've been 'handling it' for weeks now. I'm starting to get concerned."
-  },
-  {
-    "u1": "Come on, you're not my mom. I said I'm working on it!",
-    "u2": "My friend, don't get cheeky with me, what exactly is going on in that project that gets you so worked up each time the subject arises?"
+          <t>{
+  "context": "You've just introduced Steve to your work colleagues and everybody seems to love him because he is funny, witty, and charming.  Steve says, \"hey, this is fun. I'm having a great time.\"",
+  "reply": "I knew you'd like them!"
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "You know, everyone's been asking me about you!",
+    "u2": "Oh really?"
+  },
+  {
+    "u1": "I told them you were a genius and a great person to have as a friend.",
+    "u2": "Thanks, Steve. That's sweet."
+  },
+  {
+    "u1": "I'm glad you're here. Everyone's been enjoying your company.",
+    "u2": "I knew you'd like them!"
   }
 ]</t>
         </is>
@@ -5729,7 +5393,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>203_2086</t>
+          <t>129_1007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5739,31 +5403,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>That is hilarious Steve. Great imagination.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I just saw a dog wearing a tiny top hat. It was so cute!",
-    "u2": "That's adorable, Steve! You always find the cutest things."
-  },
-  {
-    "u1": "I'm thinking of drawing a cat with a hat. What do you think?",
-    "u2": "That sounds like a fun idea! I'd love to see it."
-  },
-  {
-    "u1": "Instead, I drew a horse with a carrot tied to its forehead. Steve says, 'now that's a unicorn!'",
-    "u2": "That is hilarious Steve. Great imagination."
+          <t>{
+  "context": "You are helping Steve move into a new apartment. After an hour, you realize that Steve is only carrying light stuff and you are doing all the heavy lifting.  Steve says, \"ugh, moving is always so stressful and chaotic...\"",
+  "reply": "Yes, this bit is always long to do."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Steve: Hey, can you grab that heavy box for me? I'm struggling here.",
+    "u2": "Sure, man. I've got you."
+  },
+  {
+    "u1": "Thanks, bro. You're a lifesaver.",
+    "u2": "No problem, Steve. We're in this together."
+  },
+  {
+    "u1": "You know, I'm starting to feel the weight of all this stuff.",
+    "u2": "Yes, this bit is always long to do."
   }
 ]</t>
         </is>
@@ -5772,28 +5434,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>205_2074</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Steve: Hey, look what I made! It's a new ketchup and mustard smoothie!",
+    "u2": "Steve, what are you doing? That's not a smoothie."
+  },
+  {
+    "u1": "Steve: No, really! It's delicious! Try it!",
+    "u2": "Steve, please don't mix ketchup and mustard together. It's not food."
+  },
+  {
+    "u1": "Steve: Hey, look, I made something delicious!",
+    "u2": "go sit down and get a drink of water and stop making a damn mess in my kitchen"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>207_2112</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are watching TV with Steve. Whenever you set the volume to an odd number, Steve takes the remote control away from you and sets the volume to an even number.",
+  "reply": "Steve, have you ever considered seeing a therapist about OCD?"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I know, right? It's like you're always trying to make me lose my mind!",
+    "u2": "Oh, come on, Steve. You're the one who's always making me crazy!"
+  },
+  {
+    "u1": "I'm just trying to keep the peace, u2. You're the one who's always changing the volume!",
+    "u2": "Well, maybe if you didn't take the remote away every time I set it to an odd number, I wouldn't have to keep doing it!"
+  },
+  {
+    "u1": "You know, sometimes I think you're just trying to provoke me. Why do you insist on setting it to odd numbers?",
+    "u2": "Steve, have you ever considered seeing a therapist about OCD?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>215_2027</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Steve says to you, "have you noticed that kids these days drink energy drinks all the time? That can't be healthy." At the same time, you notice that Steve is getting his 8th cup of coffee of the day.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve.</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve says to you, \"have you noticed that kids these days drink energy drinks all the time? That can't be healthy.\" At the same time, you notice that Steve is getting his 8th cup of coffee of the day.",
+  "reply": "Haha, no less healthy than drinking coffee constantly. Don't energy drinks and coffee both have caffeine in them anyway? You're such a hypocrite, Steve."
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -5812,31 +5554,29 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>221_2069</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, "look, it must be an alien because humans can't do that. What else could it be?"</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>I don't know, but it might be.  Did you see the circles that farmer found in his field?</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is obsessed with UFOs and often talks to you about it even though you don't care. He shows you a video from a website about aliens. And he says, \"look, it must be an alien because humans can't do that. What else could it be?\"",
+  "reply": "I don't know, but it might be.  Did you see the circles that farmer found in his field?"
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -5855,31 +5595,29 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>222_2046</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, "I finally found one you'll like! This one is really good. Come on!"</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>I doubt it but go ahead.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve is a fan of Bulgarian folk music. Every week, he finds a different song and plays it on his phone and says, \"I finally found one you'll like! This one is really good. Come on!\"",
+  "reply": "I doubt it but go ahead."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -5898,74 +5636,29 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>229_2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>You and Steve are drinking at a bar. You both have had about 5 beers so far. Every single time you stand up to get more beer, Steve stops you and says, "get another one for me too, will you?"</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sure, but you owe me.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "Get another one for me too, will you?",
-    "u2": "You always do this."
-  },
-  {
-    "u1": "I know, but you're the one who's buying.",
-    "u2": "Yeah, but you're always the one who's drinking more."
-  },
-  {
-    "u1": "Get another one for me too, will you?",
-    "u2": "Sure, but you owe me."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>258_2046</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say "why can't you get it yourself?", he simply says, "oh, no reason. I just wanted you to do it for me."</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Well tough, get it yourself.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Steve asks you to get him some coffee from a coffee shop nearby. But he doesn't seem to be particularly busy right now. When you say \"why can't you get it yourself?\", he simply says, \"oh, no reason. I just wanted you to do it for me.\"",
+  "reply": "Well tough, get it yourself."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -5984,31 +5677,29 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>267_2115</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>You walk into the room and Steve is there and Steve says "hi!"</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>hello</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You walk into the room and Steve is there and Steve says \"hi!\"",
+  "reply": "hello"
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -6027,49 +5718,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>271_2056</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>You are going to a party later today. You ask if Steve wants to join. He says, "I'm interested. When does the party start?"</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>about 9pm</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm interested. How long will it last?",
-    "u2": "Not sure, maybe a few hours?"
-  },
-  {
-    "u1": "Can I come with you?",
-    "u2": "Of course, I'll pick you up at 8:30?"
-  },
-  {
-    "u1": "Thanks, what time does the party start?",
-    "u2": "about 9pm"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -6083,18 +5731,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>I'm letting you win!</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "I'm letting you win!"
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>[
   {
@@ -6126,18 +5772,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, "come on, you can do better than that!"</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>yaaaa because you are on the winning streak today enjoy while it last</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
+          <t>{
+  "context": "You and Steve are playing a new video game and you are totally losing to him. Steve teases you by saying, \"come on, you can do better than that!\"",
+  "reply": "yaaaa because you are on the winning streak today enjoy while it last"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>[
   {
@@ -6169,18 +5813,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>yawn</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+          <t>{
+  "context": "Steve talks about the differences between two types of dinosaurs for an hour. You absolutely don't care about the topic.",
+  "reply": "yawn"
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>[
   {
@@ -6212,18 +5854,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, "so, how is my puppy doing?"</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
+          <t>{
+  "context": "You were watching Steve's new puppy for a week while he was traveling in Italy. The puppy made a total mess out of your apartment.  Clearly, Steve did not train the puppy properly.  Steve texts you and says, \"so, how is my puppy doing?\"",
+  "reply": "I think the puppy didn't like me it ran away. Kidding just know that you owe me a lot of money."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>[
   {
@@ -6255,18 +5895,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, "now that's a unicorn!"</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>an unusual one!</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
+          <t>{
+  "context": "Steve likes to draw. He says he is going to draw a unicorn. Instead, he draws a horse with a carrot tied to its forehead. Steve says, \"now that's a unicorn!\"",
+  "reply": "an unusual one!"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>[
   {
@@ -6288,7 +5926,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>205_2045</t>
+          <t>205_2055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6298,31 +5936,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says "hey, look, I made something delicious!"</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Knock yourself out, just don't expect me to try it!</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "Hey, I mixed some stuff together, wanna try it?",
-    "u2": "No, thanks. I'm good."
-  },
-  {
-    "u1": "Oh, come on! It's not that bad.",
-    "u2": "Yeah, yeah, I'm sure it's delicious. Just not for me."
-  },
-  {
-    "u1": "You're missing out!",
-    "u2": "Knock yourself out, just don't expect me to try it!"
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Yeah nah I'm good, you can have that yourself!"
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Steve: You know what? I think I've got this party started off right!",
+    "u2": "Yeah, sure, it's your party."
+  },
+  {
+    "u1": "And I've got the perfect drink for you too!",
+    "u2": "I'm good, Steve, you know that."
+  },
+  {
+    "u1": "Just try it, it's a real party starter!",
+    "u2": "Yeah nah I'm good, you can have that yourself!"
   }
 ]</t>
         </is>
@@ -6341,18 +5977,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, "wow, you really should watch how you spend your money."</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours.</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
+          <t>{
+  "context": "Steve recently ended up paying 120 dollars for something he bought on Amazon because he forgot to send it back and missed the free-return period. Today, you bought an expensive bag of coffee for 40 dollars from a hipster cafe in town. When Steve learns about how expensive the coffee was, he says, \"wow, you really should watch how you spend your money.\"",
+  "reply": "Lol, said someone who ended up paying over a hundred bucks because he missed the free-return period on Amazon. I could have bought 3 bags of coffee rather than seeing you wasting money on that thing of yours."
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>[
   {
@@ -6384,18 +6018,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say "I don't care. Just pick one and get it over with," Steve says "I don't need a haircut right now. But I want to be well-informed when I do!"</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
+          <t>{
+  "context": "Steve has recently been interested in trendy hairstyles. He keeps showing you pictures of different hairstyles and asks for your opinion. When you say \"I don't care. Just pick one and get it over with,\" Steve says \"I don't need a haircut right now. But I want to be well-informed when I do!\"",
+  "reply": "Then why are you annoying me with trendy haircuts? You trying to tell me summit Steve?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>[
   {
@@ -6417,28 +6049,67 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>237_2038</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>{
+  "context": "You are having a small party at your house. Steve, a little tipsy, starts mixing ketchup, mustard, potato chips, and orange juice and says \"hey, look, I made something delicious!\"",
+  "reply": "Did you really need to add orange juice to it?"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "Hey, I thought it would be good to mix some sweetness in there!",
+    "u2": "That's not exactly sweetness, Steve."
+  },
+  {
+    "u1": "Oh come on, it's a party! We can try anything!",
+    "u2": "Well, I guess that's one way to look at it."
+  },
+  {
+    "u1": "And I thought it would be a nice twist!",
+    "u2": "Did you really need to add orange juice to it?"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>242_2095</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, "jeez, people are so unreliable!"</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>yeah imagine that eh?</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CSC</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>{
+  "context": "Yesterday you had lunch with Steve at a cash-only restaurant. You had to pay for him because he didn't have any cash. He said he would pay you back later. A few days later, while still not having paid you back, Steve complains to you that his friend hasn't given back the bike he borrowed from Steve and says, \"jeez, people are so unreliable!\"",
+  "reply": "yeah imagine that eh?"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
@@ -6452,49 +6123,6 @@
   {
     "u1": "I mean, I lent it to him, and he hasn't even bothered to pay you back for lunch yet.",
     "u2": "yeah imagine that eh?"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>248_2085</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CSC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Steve is learning French. Whenever Steve meets a French person, he speaks French to them but he is very bad at it. You and Steve met a person who doesn't speak English that well. And Steve whispers to you, "that person should work on their English, don't you think?"</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>I think you should work on your french</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been practicing French, but I'm not sure I'm getting better.",
-    "u2": "That's great, Steve! How's it going?"
-  },
-  {
-    "u1": "I'm still struggling, to be honest. I keep getting mixed up with the gender of the articles.",
-    "u2": "Oh, that's a tough one! It'll come with time."
-  },
-  {
-    "u1": "Yeah, I guess. I just wish I could speak to that French person I met yesterday without making a fool of myself.",
-    "u2": "I think you should work on your french"
   }
 ]</t>
         </is>
@@ -6511,7 +6139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6527,20 +6155,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>post</t>
+          <t>original_turn</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>reply</t>
+          <t>aggregate_irony_label</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>aggregate_irony_label</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>dialogue</t>
         </is>
@@ -6559,18 +6182,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>@USER It's cruel and it's false</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
+          <t>{
+  "post": "@USER It's cruel and it's false",
+  "reply": "@USER Just lazy. My aunt quit smoking young, ate like an athlete in training, and ran all over her NH farm. My mother never smoked, loved sweets, ran all over the  Methuen Mall. My grandfather got sober, never stopped moving, ate what he could afford. They were dealt their destiny."
+}</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>[
   {
@@ -6602,19 +6223,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&gt;the Commonwealth was trying to provide the manifest "as urgently as they possibly can"
-What the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>I know, this is totally unacceptable considering how hard Peter Dutton touts national security.</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+          <t>{
+  "post": "&gt;the Commonwealth was trying to provide the manifest \"as urgently as they possibly can\"\nWhat the actual fuck?  Manifests are compiled and submitted by airlines by law.  The Commonwealth government is not able to get a copy of a few pages done quickly?  And the Commonwealth is only today thinking about a process to deal with this request?  God we're so stupid.",
+  "reply": "I know, this is totally unacceptable considering how hard Peter Dutton touts national security."
+}</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>[
   {
@@ -6646,18 +6264,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road.</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>{
+  "post": "It's actually illegal (UK) for drivers to do this on purpose to pedestrians now.",
+  "reply": "I don’t think they did it on purpose, per se, but they definitely could’ve reduced the amount of splash by being aware of the road."
+}</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>[
   {
@@ -6689,28 +6305,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Q3. What is the resolution of the #GalaxyZFlip3 main camera?
-A. 8MP
-B. 10MP
-C. 12MP
-D. 16MP
-#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>@USER Q3) C. 12MP ?
-#GalaxyZFlip3 
-#FlipAtFlipkart #GalaxyZFlip3 
-#GalaxyZFlip3Giveaway 
-#stufflistingsarmy 
-@stufflistings</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
+          <t>{
+  "post": "Q3. What is the resolution of the #GalaxyZFlip3 main camera?\nA. 8MP\nB. 10MP\nC. 12MP\nD. 16MP\n\n#FlipAtFlipkart #GalaxyZFlip3 #GalaxyZFlip3Giveaway #stufflistingsarmy",
+  "reply": "@USER Q3) C. 12MP ?\n\n#GalaxyZFlip3 \n#FlipAtFlipkart #GalaxyZFlip3 \n#GalaxyZFlip3Giveaway \n#stufflistingsarmy \n@stufflistings"
+}</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>[
   {
@@ -6742,18 +6346,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Okay that is HELLA interesting</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+          <t>{
+  "post": "Kurt Cobain. Interestingly my uncle did his autopsy and even has pictures from it that he took home! (Unfortunately these picture are across the country at my grandparents house)",
+  "reply": "Okay that is HELLA interesting"
+}</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>[
   {
@@ -6785,18 +6387,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+          <t>{
+  "post": "@USER Im so proud of you. I think its going to help your bipolar a lot. Congratulations. Im here if you ever need me. My dear friend, Never Ever Give Up. The miracle is right around the corner. ❤❤?",
+  "reply": "@USER Thank you so much for taking the time to just be there, you have a friend here if you ever needed me, this job is what I needed, I feel so amazing l, all the stress of my old job was killing me"
+}</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>[
   {
@@ -6828,18 +6428,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I have COVID, I live alone and I am very sad. Please send pictures of your dogs.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
+          <t>{
+  "post": "I have COVID, I live alone and I am very sad. Please send pictures of your dogs.",
+  "reply": "@USER So sorry, its horrible. Get yourself onto  @USER and binge feel good programme's like #DerryGirls #WorkinMoms Feel better soon."
+}</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>[
   {
@@ -6871,18 +6469,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Please tell me that's photo-shopped.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>It's photoshopped.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+          <t>{
+  "post": "Please tell me that's photo-shopped.",
+  "reply": "It's photoshopped."
+}</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>[
   {
@@ -6914,18 +6510,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+          <t>{
+  "post": "I literally passed a cafe an hour ago with himself sat in the window with other people and he looked stressed to fuck",
+  "reply": "I'm sure he's not worried about his staff members who he laid off. Click farms are nonsensical. If any account or post has a high number of likes or followers I'm always wondering how many actual real people liked it or followed it and how many bots did the same."
+}</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>[
   {
@@ -6957,24 +6551,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>The people of Scotland had a vote on devolution in 1997.
-They voted clearly in support of devolution and that vote has been respected with it's implementation.
-Time for another vote to see if they still want devolution.
-A lot has changed since then.
-Is that how it works?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>@USER One question . 
-SHOULD SCOTLAND BE INDEPENDENT.
-Ban all coverage from any political parties, let the people decide with their own conscience.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+          <t>{
+  "post": "The people of Scotland had a vote on devolution in 1997.\nThey voted clearly in support of devolution and that vote has been respected with it's implementation.\nTime for another vote to see if they still want devolution.\nA lot has changed since then.\nIs that how it works?",
+  "reply": "@USER One question . \n\nSHOULD SCOTLAND BE INDEPENDENT.\n\nBan all coverage from any political parties, let the people decide with their own conscience."
+}</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>[
   {
@@ -6996,7 +6582,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15884021082988968900_244264240786502817</t>
+          <t>15552971381088866001_11888329237387000433</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -7006,32 +6592,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Counting calories as a strategy to lose weight generally never works.   
-Plus your eating low calorie ranch,  which is probably worse for your health at the end of the day.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been trying to lose some weight and I've heard that counting calories is a good way to do it. What do you think?",
-    "u2": "I'm not sure if counting calories is the best way to lose weight. It often leads to restrictive eating, and that can be unhealthy in the long run."
-  },
-  {
-    "u1": "Really? I thought it was just about balancing what you eat and how much you exercise. I've been trying to eat more vegetables as snacks because they're low in calories.",
-    "u2": "That's a good start, but you should be careful with low-calorie dressings like ranch. They might not be as healthy as you think."
-  },
-  {
-    "u1": "The secret is to count your calories for everything you eat. Calories in - calories out. If you eat an actual portion of ice cream, that’s maybe like 120 calories which isn’t too bad. But if you eat the entire tub or a full bowl you’re in trouble. If you’re looking for casual snacks: veggies. I do celery with low calorie ranch, cherry tomatoes, broccoli, or carrots. I can eat so much for a relatively low amount of calories and it’s very satisfying. Also cut out all soda or drinks except water.",
-    "u2": "Counting calories as a strategy to lose weight generally never works.   \nPlus your eating low calorie ranch,  which is probably worse for your health at the end of the day."
+          <t>{
+  "post": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+  "reply": "Lol. Nice one."
+}</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I'm pretty sure I dropped something valuable in New South Wales recently. Can you help me find it?",
+    "u2": "Oh, really? What did you drop?"
+  },
+  {
+    "u1": "It's a small, unique item that I can't afford to replace. I'm really hoping someone found it and might want to return it.",
+    "u2": "I see. Well, I might be able to help you keep an eye out."
+  },
+  {
+    "u1": "Pretty sure that’s mine. I dropped one in nsw recently... please pm to return /s",
+    "u2": "Lol. Nice one."
   }
 ]</t>
         </is>
@@ -7040,7 +6623,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16479877604240977630_5093588245350490870</t>
+          <t>15878862390442679669_5355962305897979354</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -7050,31 +6633,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>I guess it had the same sort of effect</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I heard there was a maintenance issue on the tracks today.",
-    "u2": "Yeah, I saw some delays on my commute."
-  },
-  {
-    "u1": "I wonder what caused that.",
-    "u2": "It might have been something on the tracks."
-  },
-  {
-    "u1": "It wasn't a train lol...small maintenance vehicle, but it messed up a lot of train lines.",
-    "u2": "I guess it had the same sort of effect"
+          <t>{
+  "post": "It’s Official! I’m Irish!",
+  "reply": "Paper Irish*"
+}</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "- I've always loved Irish culture, and now I finally get to experience it firsthand!",
+    "u2": "That's great! How did you get into it?"
+  },
+  {
+    "u1": "- I've been reading about Irish history and traditions. It's fascinating!",
+    "u2": "You're really passionate about it. So, have you applied for citizenship?"
+  },
+  {
+    "u1": "It’s Official! I’m Irish!",
+    "u2": "Paper Irish*"
   }
 ]</t>
         </is>
@@ -7083,28 +6664,149 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>16839627327148929126_1096202613083543084</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Resulting riots in carlow have caused literally dozens of euros in damage",
+  "reply": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+}</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I heard there were some disturbances in Carlow last night. Any idea what's happening?",
+    "u2": "Oh, you mean the protest? It's just a bunch of people complaining about the new tax laws."
+  },
+  {
+    "u1": "Yeah, I saw some reports about it. They say it's getting a bit heated.",
+    "u2": "Well, you know how people can get when they're upset about money."
+  },
+  {
+    "u1": "Resulting riots in carlow have caused literally dozens of euros in damage",
+    "u2": "It will take Michael weeks of dole payments to replace the broken window on his 2004 Toyota."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>17330182337901269040_13248394110397545835</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{
+  "post": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+  "reply": "@USER And stay empty stomach, jobless."
+}</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "u1: Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+    "u2": "@USER And stay empty stomach, jobless."
+  },
+  {
+    "u1": "u1: I just heard that Congressmen are planning to visit Statue of Unity. Have you heard anything about it?",
+    "u2": "u2: Yes, I have. They are planning to visit, but I don't think they will."
+  },
+  {
+    "u1": "Ask Congressmen if they have visited Statue of Unity; have a big heart and visit Sardar Patel's memorial: PM Modi",
+    "u2": "@USER And stay empty stomach, jobless."
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>17457646054318905579_2168687590666378141</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>{
+  "post": "What is one company you'll never do business with because of their horrible politics?",
+  "reply": "@USER The Catholic Church"
+}</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "\"u1: How do you feel about the recent political climate?",
+    "u2": "u2: It's quite concerning, to be honest."
+  },
+  {
+    "u1": "I agree. What do you think about the role of corporations in politics?",
+    "u2": "u2: Some companies are way too involved, it's not right."
+  },
+  {
+    "u1": "What is one company you'll never do business with because of their horrible politics?",
+    "u2": "@USER The Catholic Church"
+  }
+]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2897406339829303586_14245870496726293002</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>@USER You missed  @USER  of the list.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>@USER  @USER Nah Jim bounces well.</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MultiPICo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>{
+  "post": "@USER You missed  @USER  of the list.",
+  "reply": "@USER  @USER Nah Jim bounces well."
+}</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>[
   {
@@ -7123,140 +6825,10 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>3359863154989737995_1780717056669965981</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Arsenic byproduct of mining</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>That doesn't seem very fast acting.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "u1: Did you know that arsenic is often found in mining waste?",
-    "u2": "I didn't realize that."
-  },
-  {
-    "u1": "It's a common byproduct of mining operations.",
-    "u2": "That's interesting. What about its effects?"
-  },
-  {
-    "u1": "Arsenic byproduct of mining",
-    "u2": "That doesn't seem very fast acting."
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>3387143640398978761_8608797291134632917</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dear  @USER 
- I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm back from the National Games and I'm still reeling from the experience. The staff at the airport were so rude and unhelpful.",
-    "u2": "That's unfortunate. What happened?"
-  },
-  {
-    "u1": "They charged me a ridiculous amount for excess baggage. It was just the medals and goodies I won!",
-    "u2": "That's ridiculous! What airline were you with?"
-  },
-  {
-    "u1": "Dear  @USER \n\n I was returning from the National Games held in Gujarat, and the staff not only behaved badly, but also charged us a hefty amount for excess baggage which was the medals and goodies that we athletes had won.",
-    "u2": "@USER  @USER What do you expect from a third class airlines.? Indigo airlines is worse than the village town bus"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4153912052076221148_13253936608490326173</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MultiPICo</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>@USER Except for the fact that he is a cheat</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've seen some of the comments online about Porteous. It's quite disturbing.",
-    "u2": "I think he deserves it. He's been caught cheating before."
-  },
-  {
-    "u1": "I disagree. Everyone makes mistakes, but he's a promising young player. I don't think he's a cheat.",
-    "u2": "Well, I've heard he's been caught multiple times."
-  },
-  {
-    "u1": "The targeted abuse towards Porteous, a young player with a promising future, is disgusting. Media in this country do no favours in helping the game progress. Don't mind him being seen as a 'pantomine villain' but the current 'cheating' narrative is way over the line.",
-    "u2": "@USER Except for the fact that he is a cheat"
-  }
-]</t>
-        </is>
-      </c>
-    </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4406816020059779237_11047491654451679497</t>
+          <t>3323520100287981446_1413281847757410776</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7266,31 +6838,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jason Momoa, i'm straight but if i had to, that guy could tear me up.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Ouch your butt</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I just saw Jason Momoa in that new movie, he's got some serious swag.",
-    "u2": "Yeah, he's got that 'Aquaman' vibe going on."
-  },
-  {
-    "u1": "I'm straight, but if I had to, that guy could definitely take me down.",
-    "u2": "Ouch, that's some serious power."
-  },
-  {
-    "u1": "Jason Momoa, i'm straight but if i had to, that guy could tear me up.",
-    "u2": "Ouch your butt"
+          <t>{
+  "post": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+  "reply": "And are a security nightmare"
+}</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I've been looking into smart home devices and I think they could make our lives easier.",
+    "u2": "Like what?"
+  },
+  {
+    "u1": "Well, there are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone.",
+    "u2": "That sounds convenient."
+  },
+  {
+    "u1": "There are kettles and toasters that hook into your WiFi that can be set to operate at a particular time or be controlled by your phone however you're still going to have to get out of bed to make tea and butter your toast",
+    "u2": "And are a security nightmare"
   }
 ]</t>
         </is>
@@ -7299,7 +6869,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5529300028522332247_13762710351753037022</t>
+          <t>4377701867540598223_265041111922432154</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7309,31 +6879,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fuck me! The Russian Gollum has announced partial mobilisation!</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I'm worried about the news from Russia. Have you heard anything?",
-    "u2": "Yeah, I caught a bit on the news. It's not looking good."
-  },
-  {
-    "u1": "I saw that Putin announced some kind of mobilization. It's scary.",
-    "u2": "You're right, he's been making some pretty wild claims. I don't know what to make of it."
-  },
-  {
-    "u1": "Fuck me! The Russian Gollum has announced partial mobilisation!",
-    "u2": "@USER You should have heard the Russian bloke screaming on Radio 4 ? and I thought out politicians were batshit!"
+          <t>{
+  "post": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+  "reply": "What's their excuse this time?"
+}</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I've been hearing about a lot of shouting at the Metro Station lately. What's been happening?",
+    "u2": "Well, it's not exactly shouting, but some people have been loudly expressing their opinions."
+  },
+  {
+    "u1": "Oh really? What's the issue this time?",
+    "u2": "It seems to be about that new policy change they've made."
+  },
+  {
+    "u1": "People are now justifying \"Goli Maro\" shouting at Metro Station.",
+    "u2": "What's their excuse this time?"
   }
 ]</t>
         </is>
@@ -7342,7 +6910,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>848231709404136191_17349058094094593523</t>
+          <t>5484529351205990135_6006195789051494887</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -7352,31 +6920,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How many roads must a man walk down?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>The only word I know is grunt and I can't spell it.</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[
-  {
-    "u1": "I've been thinking about life lately.",
-    "u2": "Me too. It's a bit of a grind sometimes."
-  },
-  {
-    "u1": "I've been wondering about all the paths we take in life.",
-    "u2": "Yeah, like how some paths lead to grunt work and others to something more."
-  },
-  {
-    "u1": "How many roads must a man walk down?",
-    "u2": "The only word I know is grunt and I can't spell it."
+          <t>{
+  "post": "I know it says great, but all I see is ordinary Britain.",
+  "reply": "Ordinary Britain is in France"
+}</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>[
+  {
+    "u1": "I've been to Paris, but I didn't get the 'great' part.",
+    "u2": "Well, what did you expect? It's not London."
+  },
+  {
+    "u1": "I guess I just expected something more... extraordinary.",
+    "u2": "I suppose that's subjective. Some people find Paris ordinary."
+  },
+  {
+    "u1": "I know it says great, but all I see is ordinary Britain.",
+    "u2": "Ordinary Britain is in France"
   }
 ]</t>
         </is>
@@ -7395,18 +6961,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>your son is brilliant</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="inlineStr">
+          <t>{
+  "post": "My son came home from a party(obviously drunk) he had to throw up and he said he was ill from the food.",
+  "reply": "your son is brilliant"
+}</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>[
   {
